--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -721,25 +721,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1854900</v>
+        <v>257900</v>
       </c>
       <c r="E8" s="3">
-        <v>1398100</v>
+        <v>194400</v>
       </c>
       <c r="F8" s="3">
-        <v>2034400</v>
+        <v>282800</v>
       </c>
       <c r="G8" s="3">
-        <v>3098600</v>
+        <v>430800</v>
       </c>
       <c r="H8" s="3">
-        <v>4281300</v>
+        <v>595200</v>
       </c>
       <c r="I8" s="3">
-        <v>3422900</v>
+        <v>475900</v>
       </c>
       <c r="J8" s="3">
-        <v>1346700</v>
+        <v>187200</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -760,25 +760,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1105600</v>
+        <v>153700</v>
       </c>
       <c r="E9" s="3">
-        <v>1201300</v>
+        <v>167000</v>
       </c>
       <c r="F9" s="3">
-        <v>1146400</v>
+        <v>159400</v>
       </c>
       <c r="G9" s="3">
-        <v>1483900</v>
+        <v>206300</v>
       </c>
       <c r="H9" s="3">
-        <v>1943100</v>
+        <v>270100</v>
       </c>
       <c r="I9" s="3">
-        <v>1409900</v>
+        <v>196000</v>
       </c>
       <c r="J9" s="3">
-        <v>442700</v>
+        <v>61500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -799,25 +799,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>749300</v>
+        <v>104200</v>
       </c>
       <c r="E10" s="3">
-        <v>196800</v>
+        <v>27400</v>
       </c>
       <c r="F10" s="3">
-        <v>888000</v>
+        <v>123400</v>
       </c>
       <c r="G10" s="3">
-        <v>1614700</v>
+        <v>224500</v>
       </c>
       <c r="H10" s="3">
-        <v>2338200</v>
+        <v>325100</v>
       </c>
       <c r="I10" s="3">
-        <v>2013000</v>
+        <v>279800</v>
       </c>
       <c r="J10" s="3">
-        <v>904000</v>
+        <v>125700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -855,25 +855,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3">
-        <v>10000</v>
+        <v>1400</v>
       </c>
       <c r="G12" s="3">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="H12" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="I12" s="3">
-        <v>4800</v>
+        <v>700</v>
       </c>
       <c r="J12" s="3">
-        <v>8500</v>
+        <v>1200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -936,13 +936,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>12000</v>
+        <v>1700</v>
       </c>
       <c r="F14" s="3">
-        <v>24800</v>
+        <v>3400</v>
       </c>
       <c r="G14" s="3">
-        <v>25300</v>
+        <v>3500</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>57000</v>
+        <v>7900</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -972,25 +972,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2200</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>3800</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3">
-        <v>10900</v>
+        <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>13300</v>
+        <v>1800</v>
       </c>
       <c r="I15" s="3">
-        <v>10800</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1025,25 +1025,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1682300</v>
+        <v>233900</v>
       </c>
       <c r="E17" s="3">
-        <v>1304400</v>
+        <v>181300</v>
       </c>
       <c r="F17" s="3">
-        <v>1871700</v>
+        <v>260200</v>
       </c>
       <c r="G17" s="3">
-        <v>2377600</v>
+        <v>330500</v>
       </c>
       <c r="H17" s="3">
-        <v>3123500</v>
+        <v>434200</v>
       </c>
       <c r="I17" s="3">
-        <v>2614200</v>
+        <v>363400</v>
       </c>
       <c r="J17" s="3">
-        <v>1058600</v>
+        <v>147200</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1064,25 +1064,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>172600</v>
+        <v>24000</v>
       </c>
       <c r="E18" s="3">
-        <v>93800</v>
+        <v>13000</v>
       </c>
       <c r="F18" s="3">
-        <v>162700</v>
+        <v>22600</v>
       </c>
       <c r="G18" s="3">
-        <v>721000</v>
+        <v>100200</v>
       </c>
       <c r="H18" s="3">
-        <v>1157700</v>
+        <v>160900</v>
       </c>
       <c r="I18" s="3">
-        <v>808700</v>
+        <v>112400</v>
       </c>
       <c r="J18" s="3">
-        <v>288000</v>
+        <v>40000</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1159,25 +1159,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>174800</v>
+        <v>24300</v>
       </c>
       <c r="E21" s="3">
-        <v>97600</v>
+        <v>13600</v>
       </c>
       <c r="F21" s="3">
-        <v>168700</v>
+        <v>23500</v>
       </c>
       <c r="G21" s="3">
-        <v>731900</v>
+        <v>101800</v>
       </c>
       <c r="H21" s="3">
-        <v>1171000</v>
+        <v>162800</v>
       </c>
       <c r="I21" s="3">
-        <v>819500</v>
+        <v>113900</v>
       </c>
       <c r="J21" s="3">
-        <v>294600</v>
+        <v>41000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1237,25 +1237,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>172600</v>
+        <v>24000</v>
       </c>
       <c r="E23" s="3">
-        <v>93800</v>
+        <v>13000</v>
       </c>
       <c r="F23" s="3">
-        <v>162700</v>
+        <v>22600</v>
       </c>
       <c r="G23" s="3">
-        <v>721000</v>
+        <v>100200</v>
       </c>
       <c r="H23" s="3">
-        <v>1157700</v>
+        <v>160900</v>
       </c>
       <c r="I23" s="3">
-        <v>808700</v>
+        <v>112400</v>
       </c>
       <c r="J23" s="3">
-        <v>288000</v>
+        <v>40000</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1276,25 +1276,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>37200</v>
+        <v>5200</v>
       </c>
       <c r="E24" s="3">
-        <v>28600</v>
+        <v>4000</v>
       </c>
       <c r="F24" s="3">
-        <v>47800</v>
+        <v>6700</v>
       </c>
       <c r="G24" s="3">
-        <v>186400</v>
+        <v>25900</v>
       </c>
       <c r="H24" s="3">
-        <v>296800</v>
+        <v>41300</v>
       </c>
       <c r="I24" s="3">
-        <v>276000</v>
+        <v>38400</v>
       </c>
       <c r="J24" s="3">
-        <v>52600</v>
+        <v>7300</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1354,25 +1354,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>135400</v>
+        <v>18800</v>
       </c>
       <c r="E26" s="3">
-        <v>65200</v>
+        <v>9100</v>
       </c>
       <c r="F26" s="3">
-        <v>114900</v>
+        <v>16000</v>
       </c>
       <c r="G26" s="3">
-        <v>534600</v>
+        <v>74300</v>
       </c>
       <c r="H26" s="3">
-        <v>860900</v>
+        <v>119700</v>
       </c>
       <c r="I26" s="3">
-        <v>532700</v>
+        <v>74100</v>
       </c>
       <c r="J26" s="3">
-        <v>235400</v>
+        <v>32700</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1393,25 +1393,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>135400</v>
+        <v>18800</v>
       </c>
       <c r="E27" s="3">
-        <v>65200</v>
+        <v>9100</v>
       </c>
       <c r="F27" s="3">
-        <v>114900</v>
+        <v>16000</v>
       </c>
       <c r="G27" s="3">
-        <v>534600</v>
+        <v>74300</v>
       </c>
       <c r="H27" s="3">
-        <v>860900</v>
+        <v>119700</v>
       </c>
       <c r="I27" s="3">
-        <v>532700</v>
+        <v>74100</v>
       </c>
       <c r="J27" s="3">
-        <v>235400</v>
+        <v>32700</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1627,25 +1627,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>135400</v>
+        <v>18800</v>
       </c>
       <c r="E33" s="3">
-        <v>65200</v>
+        <v>9100</v>
       </c>
       <c r="F33" s="3">
-        <v>114900</v>
+        <v>16000</v>
       </c>
       <c r="G33" s="3">
-        <v>534600</v>
+        <v>74300</v>
       </c>
       <c r="H33" s="3">
-        <v>860900</v>
+        <v>119700</v>
       </c>
       <c r="I33" s="3">
-        <v>532700</v>
+        <v>74100</v>
       </c>
       <c r="J33" s="3">
-        <v>235400</v>
+        <v>32700</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1705,25 +1705,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>135400</v>
+        <v>18800</v>
       </c>
       <c r="E35" s="3">
-        <v>65200</v>
+        <v>9100</v>
       </c>
       <c r="F35" s="3">
-        <v>114900</v>
+        <v>16000</v>
       </c>
       <c r="G35" s="3">
-        <v>534600</v>
+        <v>74300</v>
       </c>
       <c r="H35" s="3">
-        <v>860900</v>
+        <v>119700</v>
       </c>
       <c r="I35" s="3">
-        <v>532700</v>
+        <v>74100</v>
       </c>
       <c r="J35" s="3">
-        <v>235400</v>
+        <v>32700</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1822,25 +1822,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1772200</v>
+        <v>246400</v>
       </c>
       <c r="E41" s="3">
-        <v>2231400</v>
+        <v>310200</v>
       </c>
       <c r="F41" s="3">
-        <v>1960900</v>
+        <v>272600</v>
       </c>
       <c r="G41" s="3">
-        <v>1705400</v>
+        <v>237100</v>
       </c>
       <c r="H41" s="3">
-        <v>3161700</v>
+        <v>439500</v>
       </c>
       <c r="I41" s="3">
-        <v>1190400</v>
+        <v>165500</v>
       </c>
       <c r="J41" s="3">
-        <v>233100</v>
+        <v>32400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1915,10 +1915,10 @@
         <v>3</v>
       </c>
       <c r="I43" s="3">
-        <v>7900</v>
+        <v>1100</v>
       </c>
       <c r="J43" s="3">
-        <v>16500</v>
+        <v>2300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1993,10 +1993,10 @@
         <v>3</v>
       </c>
       <c r="I45" s="3">
-        <v>13100</v>
+        <v>1800</v>
       </c>
       <c r="J45" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2056,25 +2056,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11250000</v>
+        <v>1564000</v>
       </c>
       <c r="E47" s="3">
-        <v>10439900</v>
+        <v>1451300</v>
       </c>
       <c r="F47" s="3">
-        <v>9561700</v>
+        <v>1329300</v>
       </c>
       <c r="G47" s="3">
-        <v>11045900</v>
+        <v>1535600</v>
       </c>
       <c r="H47" s="3">
-        <v>15858800</v>
+        <v>2204700</v>
       </c>
       <c r="I47" s="3">
-        <v>16771700</v>
+        <v>2331600</v>
       </c>
       <c r="J47" s="3">
-        <v>7375900</v>
+        <v>1025400</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2095,25 +2095,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>32100</v>
+        <v>4500</v>
       </c>
       <c r="E48" s="3">
-        <v>19200</v>
+        <v>2700</v>
       </c>
       <c r="F48" s="3">
-        <v>24200</v>
+        <v>3400</v>
       </c>
       <c r="G48" s="3">
-        <v>47300</v>
+        <v>6600</v>
       </c>
       <c r="H48" s="3">
-        <v>19200</v>
+        <v>2700</v>
       </c>
       <c r="I48" s="3">
-        <v>22500</v>
+        <v>3100</v>
       </c>
       <c r="J48" s="3">
-        <v>18700</v>
+        <v>2600</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2134,25 +2134,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="E49" s="3">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="F49" s="3">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="G49" s="3">
-        <v>3700</v>
+        <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>4200</v>
+        <v>600</v>
       </c>
       <c r="I49" s="3">
-        <v>3300</v>
+        <v>500</v>
       </c>
       <c r="J49" s="3">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2251,25 +2251,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>76900</v>
+        <v>10700</v>
       </c>
       <c r="E52" s="3">
-        <v>21100</v>
+        <v>2900</v>
       </c>
       <c r="F52" s="3">
-        <v>75800</v>
+        <v>10500</v>
       </c>
       <c r="G52" s="3">
-        <v>16400</v>
+        <v>2300</v>
       </c>
       <c r="H52" s="3">
-        <v>217600</v>
+        <v>30300</v>
       </c>
       <c r="I52" s="3">
-        <v>112500</v>
+        <v>15600</v>
       </c>
       <c r="J52" s="3">
-        <v>55600</v>
+        <v>7700</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2329,25 +2329,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14481900</v>
+        <v>2013300</v>
       </c>
       <c r="E54" s="3">
-        <v>14386200</v>
+        <v>2000000</v>
       </c>
       <c r="F54" s="3">
-        <v>12233500</v>
+        <v>1700700</v>
       </c>
       <c r="G54" s="3">
-        <v>13026200</v>
+        <v>1810900</v>
       </c>
       <c r="H54" s="3">
-        <v>19354700</v>
+        <v>2690700</v>
       </c>
       <c r="I54" s="3">
-        <v>18215900</v>
+        <v>2532400</v>
       </c>
       <c r="J54" s="3">
-        <v>7806400</v>
+        <v>1085200</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2441,25 +2441,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>112600</v>
+        <v>15700</v>
       </c>
       <c r="E58" s="3">
-        <v>45300</v>
+        <v>6300</v>
       </c>
       <c r="F58" s="3">
-        <v>508600</v>
+        <v>70700</v>
       </c>
       <c r="G58" s="3">
-        <v>870800</v>
+        <v>121100</v>
       </c>
       <c r="H58" s="3">
-        <v>4213900</v>
+        <v>585800</v>
       </c>
       <c r="I58" s="3">
-        <v>3512100</v>
+        <v>488300</v>
       </c>
       <c r="J58" s="3">
-        <v>141700</v>
+        <v>19700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2480,25 +2480,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>247100</v>
+        <v>34400</v>
       </c>
       <c r="E59" s="3">
-        <v>194700</v>
+        <v>27100</v>
       </c>
       <c r="F59" s="3">
-        <v>204000</v>
+        <v>28400</v>
       </c>
       <c r="G59" s="3">
-        <v>212300</v>
+        <v>29500</v>
       </c>
       <c r="H59" s="3">
-        <v>731600</v>
+        <v>101700</v>
       </c>
       <c r="I59" s="3">
-        <v>452200</v>
+        <v>62900</v>
       </c>
       <c r="J59" s="3">
-        <v>147800</v>
+        <v>20500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2558,25 +2558,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7727600</v>
+        <v>1074300</v>
       </c>
       <c r="E61" s="3">
-        <v>8041900</v>
+        <v>1118000</v>
       </c>
       <c r="F61" s="3">
-        <v>5649700</v>
+        <v>785400</v>
       </c>
       <c r="G61" s="3">
-        <v>6652100</v>
+        <v>924800</v>
       </c>
       <c r="H61" s="3">
-        <v>11110900</v>
+        <v>1544600</v>
       </c>
       <c r="I61" s="3">
-        <v>12195800</v>
+        <v>1695500</v>
       </c>
       <c r="J61" s="3">
-        <v>6183800</v>
+        <v>859700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2597,25 +2597,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>73800</v>
+        <v>10300</v>
       </c>
       <c r="E62" s="3">
-        <v>151800</v>
+        <v>21100</v>
       </c>
       <c r="F62" s="3">
-        <v>396600</v>
+        <v>55100</v>
       </c>
       <c r="G62" s="3">
-        <v>359300</v>
+        <v>49900</v>
       </c>
       <c r="H62" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>2600</v>
+        <v>400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2753,25 +2753,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10595900</v>
+        <v>1473000</v>
       </c>
       <c r="E66" s="3">
-        <v>10567900</v>
+        <v>1469100</v>
       </c>
       <c r="F66" s="3">
-        <v>8492200</v>
+        <v>1180600</v>
       </c>
       <c r="G66" s="3">
-        <v>9427700</v>
+        <v>1310600</v>
       </c>
       <c r="H66" s="3">
-        <v>16309200</v>
+        <v>2267300</v>
       </c>
       <c r="I66" s="3">
-        <v>16384600</v>
+        <v>2277800</v>
       </c>
       <c r="J66" s="3">
-        <v>6687700</v>
+        <v>929700</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2965,25 +2965,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2958700</v>
+        <v>411300</v>
       </c>
       <c r="E72" s="3">
-        <v>2824300</v>
+        <v>392600</v>
       </c>
       <c r="F72" s="3">
-        <v>2759100</v>
+        <v>383600</v>
       </c>
       <c r="G72" s="3">
-        <v>2662100</v>
+        <v>370100</v>
       </c>
       <c r="H72" s="3">
-        <v>2127500</v>
+        <v>295800</v>
       </c>
       <c r="I72" s="3">
-        <v>1266600</v>
+        <v>176100</v>
       </c>
       <c r="J72" s="3">
-        <v>733900</v>
+        <v>102000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3121,25 +3121,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3886000</v>
+        <v>540200</v>
       </c>
       <c r="E76" s="3">
-        <v>3818300</v>
+        <v>530800</v>
       </c>
       <c r="F76" s="3">
-        <v>3741300</v>
+        <v>520100</v>
       </c>
       <c r="G76" s="3">
-        <v>3598500</v>
+        <v>500300</v>
       </c>
       <c r="H76" s="3">
-        <v>3045600</v>
+        <v>423400</v>
       </c>
       <c r="I76" s="3">
-        <v>1831200</v>
+        <v>254600</v>
       </c>
       <c r="J76" s="3">
-        <v>1118700</v>
+        <v>155500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>135400</v>
+        <v>18800</v>
       </c>
       <c r="E81" s="3">
-        <v>65200</v>
+        <v>9100</v>
       </c>
       <c r="F81" s="3">
-        <v>114900</v>
+        <v>16000</v>
       </c>
       <c r="G81" s="3">
-        <v>534600</v>
+        <v>74300</v>
       </c>
       <c r="H81" s="3">
-        <v>860900</v>
+        <v>119700</v>
       </c>
       <c r="I81" s="3">
-        <v>532700</v>
+        <v>74100</v>
       </c>
       <c r="J81" s="3">
-        <v>235400</v>
+        <v>32700</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3299,25 +3299,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>3800</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>10900</v>
+        <v>1500</v>
       </c>
       <c r="H83" s="3">
-        <v>13300</v>
+        <v>1800</v>
       </c>
       <c r="I83" s="3">
-        <v>10800</v>
+        <v>1500</v>
       </c>
       <c r="J83" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3533,25 +3533,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>919300</v>
+        <v>127800</v>
       </c>
       <c r="E89" s="3">
-        <v>689700</v>
+        <v>95900</v>
       </c>
       <c r="F89" s="3">
-        <v>1119600</v>
+        <v>155600</v>
       </c>
       <c r="G89" s="3">
-        <v>1299100</v>
+        <v>180600</v>
       </c>
       <c r="H89" s="3">
-        <v>1332700</v>
+        <v>185300</v>
       </c>
       <c r="I89" s="3">
-        <v>1286600</v>
+        <v>178900</v>
       </c>
       <c r="J89" s="3">
-        <v>379900</v>
+        <v>52800</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3589,25 +3589,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-89900</v>
+        <v>-12500</v>
       </c>
       <c r="E91" s="3">
-        <v>-3800</v>
+        <v>-500</v>
       </c>
       <c r="F91" s="3">
-        <v>-3200</v>
+        <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>-4400</v>
+        <v>-600</v>
       </c>
       <c r="H91" s="3">
-        <v>-14800</v>
+        <v>-2100</v>
       </c>
       <c r="I91" s="3">
-        <v>-19800</v>
+        <v>-2700</v>
       </c>
       <c r="J91" s="3">
-        <v>-15200</v>
+        <v>-2100</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3706,25 +3706,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1098200</v>
+        <v>-152700</v>
       </c>
       <c r="E94" s="3">
-        <v>-2350600</v>
+        <v>-326800</v>
       </c>
       <c r="F94" s="3">
-        <v>524100</v>
+        <v>72900</v>
       </c>
       <c r="G94" s="3">
-        <v>4936500</v>
+        <v>686300</v>
       </c>
       <c r="H94" s="3">
-        <v>641400</v>
+        <v>89200</v>
       </c>
       <c r="I94" s="3">
-        <v>-9583900</v>
+        <v>-1332400</v>
       </c>
       <c r="J94" s="3">
-        <v>-4700400</v>
+        <v>-653500</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3918,25 +3918,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-288200</v>
+        <v>-40100</v>
       </c>
       <c r="E100" s="3">
-        <v>1932600</v>
+        <v>268700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1367100</v>
+        <v>-190100</v>
       </c>
       <c r="G100" s="3">
-        <v>-7695700</v>
+        <v>-1069900</v>
       </c>
       <c r="H100" s="3">
-        <v>-2500</v>
+        <v>-400</v>
       </c>
       <c r="I100" s="3">
-        <v>9256700</v>
+        <v>1286900</v>
       </c>
       <c r="J100" s="3">
-        <v>4291100</v>
+        <v>596500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3957,25 +3957,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7800</v>
+        <v>1100</v>
       </c>
       <c r="E101" s="3">
-        <v>-1200</v>
+        <v>-200</v>
       </c>
       <c r="F101" s="3">
-        <v>-20900</v>
+        <v>-2900</v>
       </c>
       <c r="G101" s="3">
-        <v>3800</v>
+        <v>500</v>
       </c>
       <c r="H101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>-2300</v>
+        <v>-300</v>
       </c>
       <c r="J101" s="3">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3996,25 +3996,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-459300</v>
+        <v>-63800</v>
       </c>
       <c r="E102" s="3">
-        <v>270500</v>
+        <v>37600</v>
       </c>
       <c r="F102" s="3">
-        <v>255600</v>
+        <v>35500</v>
       </c>
       <c r="G102" s="3">
-        <v>-1456300</v>
+        <v>-202500</v>
       </c>
       <c r="H102" s="3">
-        <v>1971300</v>
+        <v>274000</v>
       </c>
       <c r="I102" s="3">
-        <v>957200</v>
+        <v>133100</v>
       </c>
       <c r="J102" s="3">
-        <v>-26900</v>
+        <v>-3700</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,36 +714,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>257900</v>
+        <v>253800</v>
       </c>
       <c r="E8" s="3">
-        <v>194400</v>
+        <v>256300</v>
       </c>
       <c r="F8" s="3">
-        <v>282800</v>
+        <v>193200</v>
       </c>
       <c r="G8" s="3">
-        <v>430800</v>
+        <v>281100</v>
       </c>
       <c r="H8" s="3">
-        <v>595200</v>
+        <v>428100</v>
       </c>
       <c r="I8" s="3">
-        <v>475900</v>
+        <v>591500</v>
       </c>
       <c r="J8" s="3">
+        <v>472900</v>
+      </c>
+      <c r="K8" s="3">
         <v>187200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,36 +756,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>153700</v>
+        <v>147400</v>
       </c>
       <c r="E9" s="3">
-        <v>167000</v>
+        <v>152800</v>
       </c>
       <c r="F9" s="3">
-        <v>159400</v>
+        <v>166000</v>
       </c>
       <c r="G9" s="3">
-        <v>206300</v>
+        <v>158400</v>
       </c>
       <c r="H9" s="3">
-        <v>270100</v>
+        <v>205000</v>
       </c>
       <c r="I9" s="3">
-        <v>196000</v>
+        <v>268500</v>
       </c>
       <c r="J9" s="3">
+        <v>194800</v>
+      </c>
+      <c r="K9" s="3">
         <v>61500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,36 +798,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>104200</v>
+        <v>106400</v>
       </c>
       <c r="E10" s="3">
-        <v>27400</v>
+        <v>103500</v>
       </c>
       <c r="F10" s="3">
-        <v>123400</v>
+        <v>27200</v>
       </c>
       <c r="G10" s="3">
-        <v>224500</v>
+        <v>122700</v>
       </c>
       <c r="H10" s="3">
-        <v>325100</v>
+        <v>223100</v>
       </c>
       <c r="I10" s="3">
-        <v>279800</v>
+        <v>323000</v>
       </c>
       <c r="J10" s="3">
+        <v>278100</v>
+      </c>
+      <c r="K10" s="3">
         <v>125700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,35 +861,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,36 +942,39 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>7900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -965,36 +984,39 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,35 +1044,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>233900</v>
+        <v>225400</v>
       </c>
       <c r="E17" s="3">
-        <v>181300</v>
+        <v>232400</v>
       </c>
       <c r="F17" s="3">
-        <v>260200</v>
+        <v>180200</v>
       </c>
       <c r="G17" s="3">
-        <v>330500</v>
+        <v>258600</v>
       </c>
       <c r="H17" s="3">
-        <v>434200</v>
+        <v>328500</v>
       </c>
       <c r="I17" s="3">
-        <v>363400</v>
+        <v>431500</v>
       </c>
       <c r="J17" s="3">
+        <v>361200</v>
+      </c>
+      <c r="K17" s="3">
         <v>147200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,36 +1083,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>24000</v>
+        <v>28400</v>
       </c>
       <c r="E18" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F18" s="3">
         <v>13000</v>
       </c>
-      <c r="F18" s="3">
-        <v>22600</v>
-      </c>
       <c r="G18" s="3">
-        <v>100200</v>
+        <v>22500</v>
       </c>
       <c r="H18" s="3">
-        <v>160900</v>
+        <v>99600</v>
       </c>
       <c r="I18" s="3">
-        <v>112400</v>
+        <v>160000</v>
       </c>
       <c r="J18" s="3">
+        <v>111700</v>
+      </c>
+      <c r="K18" s="3">
         <v>40000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,8 +1146,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1140,8 +1173,8 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1152,36 +1185,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>24300</v>
+        <v>28700</v>
       </c>
       <c r="E21" s="3">
-        <v>13600</v>
+        <v>24200</v>
       </c>
       <c r="F21" s="3">
-        <v>23500</v>
+        <v>13500</v>
       </c>
       <c r="G21" s="3">
-        <v>101800</v>
+        <v>23300</v>
       </c>
       <c r="H21" s="3">
-        <v>162800</v>
+        <v>101100</v>
       </c>
       <c r="I21" s="3">
-        <v>113900</v>
+        <v>161800</v>
       </c>
       <c r="J21" s="3">
+        <v>113200</v>
+      </c>
+      <c r="K21" s="3">
         <v>41000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,9 +1227,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1230,36 +1269,39 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>24000</v>
+        <v>28400</v>
       </c>
       <c r="E23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
-        <v>22600</v>
-      </c>
       <c r="G23" s="3">
-        <v>100200</v>
+        <v>22500</v>
       </c>
       <c r="H23" s="3">
-        <v>160900</v>
+        <v>99600</v>
       </c>
       <c r="I23" s="3">
-        <v>112400</v>
+        <v>160000</v>
       </c>
       <c r="J23" s="3">
+        <v>111700</v>
+      </c>
+      <c r="K23" s="3">
         <v>40000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1311,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E24" s="3">
-        <v>4000</v>
+        <v>5100</v>
       </c>
       <c r="F24" s="3">
-        <v>6700</v>
+        <v>3900</v>
       </c>
       <c r="G24" s="3">
-        <v>25900</v>
+        <v>6600</v>
       </c>
       <c r="H24" s="3">
-        <v>41300</v>
+        <v>25700</v>
       </c>
       <c r="I24" s="3">
-        <v>38400</v>
+        <v>41000</v>
       </c>
       <c r="J24" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K24" s="3">
         <v>7300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,36 +1395,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>18800</v>
+        <v>22700</v>
       </c>
       <c r="E26" s="3">
-        <v>9100</v>
+        <v>18700</v>
       </c>
       <c r="F26" s="3">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="G26" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="H26" s="3">
-        <v>119700</v>
+        <v>73900</v>
       </c>
       <c r="I26" s="3">
-        <v>74100</v>
+        <v>118900</v>
       </c>
       <c r="J26" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K26" s="3">
         <v>32700</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,36 +1437,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>18800</v>
+        <v>22700</v>
       </c>
       <c r="E27" s="3">
-        <v>9100</v>
+        <v>18700</v>
       </c>
       <c r="F27" s="3">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="G27" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="H27" s="3">
-        <v>119700</v>
+        <v>73900</v>
       </c>
       <c r="I27" s="3">
-        <v>74100</v>
+        <v>118900</v>
       </c>
       <c r="J27" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K27" s="3">
         <v>32700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,9 +1647,12 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1608,8 +1677,8 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1620,36 +1689,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>18800</v>
+        <v>22700</v>
       </c>
       <c r="E33" s="3">
-        <v>9100</v>
+        <v>18700</v>
       </c>
       <c r="F33" s="3">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="G33" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="H33" s="3">
-        <v>119700</v>
+        <v>73900</v>
       </c>
       <c r="I33" s="3">
-        <v>74100</v>
+        <v>118900</v>
       </c>
       <c r="J33" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K33" s="3">
         <v>32700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,36 +1773,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>18800</v>
+        <v>22700</v>
       </c>
       <c r="E35" s="3">
-        <v>9100</v>
+        <v>18700</v>
       </c>
       <c r="F35" s="3">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="G35" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="H35" s="3">
-        <v>119700</v>
+        <v>73900</v>
       </c>
       <c r="I35" s="3">
-        <v>74100</v>
+        <v>118900</v>
       </c>
       <c r="J35" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K35" s="3">
         <v>32700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,41 +1815,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,35 +1901,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>246400</v>
+        <v>276500</v>
       </c>
       <c r="E41" s="3">
-        <v>310200</v>
+        <v>244800</v>
       </c>
       <c r="F41" s="3">
-        <v>272600</v>
+        <v>308300</v>
       </c>
       <c r="G41" s="3">
-        <v>237100</v>
+        <v>270900</v>
       </c>
       <c r="H41" s="3">
-        <v>439500</v>
+        <v>235600</v>
       </c>
       <c r="I41" s="3">
-        <v>165500</v>
+        <v>436800</v>
       </c>
       <c r="J41" s="3">
+        <v>164500</v>
+      </c>
+      <c r="K41" s="3">
         <v>32400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,9 +1940,12 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1893,9 +1982,12 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1914,15 +2006,15 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,9 +2066,12 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1992,15 +2090,15 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2010,9 +2108,12 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2049,36 +2150,39 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1564000</v>
+        <v>1674600</v>
       </c>
       <c r="E47" s="3">
-        <v>1451300</v>
+        <v>1554300</v>
       </c>
       <c r="F47" s="3">
-        <v>1329300</v>
+        <v>1442400</v>
       </c>
       <c r="G47" s="3">
-        <v>1535600</v>
+        <v>1321000</v>
       </c>
       <c r="H47" s="3">
-        <v>2204700</v>
+        <v>1526100</v>
       </c>
       <c r="I47" s="3">
-        <v>2331600</v>
+        <v>2191000</v>
       </c>
       <c r="J47" s="3">
+        <v>2317200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1025400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2088,36 +2192,39 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="E48" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2700</v>
       </c>
-      <c r="F48" s="3">
-        <v>3400</v>
-      </c>
       <c r="G48" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="H48" s="3">
-        <v>2700</v>
+        <v>6500</v>
       </c>
       <c r="I48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,36 +2234,39 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>400</v>
+      </c>
+      <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,36 +2360,39 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10700</v>
+        <v>12700</v>
       </c>
       <c r="E52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F52" s="3">
         <v>2900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
-        <v>30300</v>
-      </c>
       <c r="I52" s="3">
-        <v>15600</v>
+        <v>30100</v>
       </c>
       <c r="J52" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K52" s="3">
         <v>7700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,36 +2444,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2013300</v>
+        <v>2260900</v>
       </c>
       <c r="E54" s="3">
-        <v>2000000</v>
+        <v>2000800</v>
       </c>
       <c r="F54" s="3">
-        <v>1700700</v>
+        <v>1987600</v>
       </c>
       <c r="G54" s="3">
-        <v>1810900</v>
+        <v>1690200</v>
       </c>
       <c r="H54" s="3">
-        <v>2690700</v>
+        <v>1799700</v>
       </c>
       <c r="I54" s="3">
-        <v>2532400</v>
+        <v>2674000</v>
       </c>
       <c r="J54" s="3">
+        <v>2516700</v>
+      </c>
+      <c r="K54" s="3">
         <v>1085200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,8 +2525,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2434,75 +2564,81 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15700</v>
+        <v>94900</v>
       </c>
       <c r="E58" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F58" s="3">
         <v>6300</v>
       </c>
-      <c r="F58" s="3">
-        <v>70700</v>
-      </c>
       <c r="G58" s="3">
-        <v>121100</v>
+        <v>70300</v>
       </c>
       <c r="H58" s="3">
-        <v>585800</v>
+        <v>120300</v>
       </c>
       <c r="I58" s="3">
-        <v>488300</v>
+        <v>582200</v>
       </c>
       <c r="J58" s="3">
+        <v>485200</v>
+      </c>
+      <c r="K58" s="3">
         <v>19700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>34400</v>
+        <v>32200</v>
       </c>
       <c r="E59" s="3">
-        <v>27100</v>
+        <v>34100</v>
       </c>
       <c r="F59" s="3">
-        <v>28400</v>
+        <v>26900</v>
       </c>
       <c r="G59" s="3">
-        <v>29500</v>
+        <v>28200</v>
       </c>
       <c r="H59" s="3">
-        <v>101700</v>
+        <v>29300</v>
       </c>
       <c r="I59" s="3">
-        <v>62900</v>
+        <v>101100</v>
       </c>
       <c r="J59" s="3">
+        <v>62500</v>
+      </c>
+      <c r="K59" s="3">
         <v>20500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,9 +2648,12 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2551,36 +2690,39 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1074300</v>
+        <v>1138900</v>
       </c>
       <c r="E61" s="3">
-        <v>1118000</v>
+        <v>1067600</v>
       </c>
       <c r="F61" s="3">
-        <v>785400</v>
+        <v>1111100</v>
       </c>
       <c r="G61" s="3">
-        <v>924800</v>
+        <v>780600</v>
       </c>
       <c r="H61" s="3">
-        <v>1544600</v>
+        <v>919100</v>
       </c>
       <c r="I61" s="3">
-        <v>1695500</v>
+        <v>1535100</v>
       </c>
       <c r="J61" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="K61" s="3">
         <v>859700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2590,36 +2732,39 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="E62" s="3">
-        <v>21100</v>
+        <v>10200</v>
       </c>
       <c r="F62" s="3">
-        <v>55100</v>
+        <v>21000</v>
       </c>
       <c r="G62" s="3">
-        <v>49900</v>
+        <v>54800</v>
       </c>
       <c r="H62" s="3">
+        <v>49600</v>
+      </c>
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,36 +2900,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1473000</v>
+        <v>1707000</v>
       </c>
       <c r="E66" s="3">
-        <v>1469100</v>
+        <v>1463900</v>
       </c>
       <c r="F66" s="3">
-        <v>1180600</v>
+        <v>1460100</v>
       </c>
       <c r="G66" s="3">
-        <v>1310600</v>
+        <v>1173300</v>
       </c>
       <c r="H66" s="3">
-        <v>2267300</v>
+        <v>1302500</v>
       </c>
       <c r="I66" s="3">
-        <v>2277800</v>
+        <v>2253300</v>
       </c>
       <c r="J66" s="3">
+        <v>2263700</v>
+      </c>
+      <c r="K66" s="3">
         <v>929700</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,36 +3128,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>411300</v>
+        <v>428800</v>
       </c>
       <c r="E72" s="3">
-        <v>392600</v>
+        <v>408800</v>
       </c>
       <c r="F72" s="3">
-        <v>383600</v>
+        <v>390200</v>
       </c>
       <c r="G72" s="3">
-        <v>370100</v>
+        <v>381200</v>
       </c>
       <c r="H72" s="3">
-        <v>295800</v>
+        <v>367800</v>
       </c>
       <c r="I72" s="3">
-        <v>176100</v>
+        <v>293900</v>
       </c>
       <c r="J72" s="3">
+        <v>175000</v>
+      </c>
+      <c r="K72" s="3">
         <v>102000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,36 +3296,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>540200</v>
+        <v>553900</v>
       </c>
       <c r="E76" s="3">
-        <v>530800</v>
+        <v>536900</v>
       </c>
       <c r="F76" s="3">
-        <v>520100</v>
+        <v>527500</v>
       </c>
       <c r="G76" s="3">
-        <v>500300</v>
+        <v>516900</v>
       </c>
       <c r="H76" s="3">
-        <v>423400</v>
+        <v>497200</v>
       </c>
       <c r="I76" s="3">
-        <v>254600</v>
+        <v>420800</v>
       </c>
       <c r="J76" s="3">
+        <v>253000</v>
+      </c>
+      <c r="K76" s="3">
         <v>155500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,41 +3380,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,36 +3427,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>18800</v>
+        <v>22700</v>
       </c>
       <c r="E81" s="3">
-        <v>9100</v>
+        <v>18700</v>
       </c>
       <c r="F81" s="3">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="G81" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="H81" s="3">
-        <v>119700</v>
+        <v>73900</v>
       </c>
       <c r="I81" s="3">
-        <v>74100</v>
+        <v>118900</v>
       </c>
       <c r="J81" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K81" s="3">
         <v>32700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,35 +3490,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,36 +3739,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>127800</v>
+        <v>235700</v>
       </c>
       <c r="E89" s="3">
-        <v>95900</v>
+        <v>127000</v>
       </c>
       <c r="F89" s="3">
-        <v>155600</v>
+        <v>95300</v>
       </c>
       <c r="G89" s="3">
-        <v>180600</v>
+        <v>154700</v>
       </c>
       <c r="H89" s="3">
-        <v>185300</v>
+        <v>179500</v>
       </c>
       <c r="I89" s="3">
-        <v>178900</v>
+        <v>184100</v>
       </c>
       <c r="J89" s="3">
+        <v>177800</v>
+      </c>
+      <c r="K89" s="3">
         <v>52800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,35 +3802,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12500</v>
+        <v>-15800</v>
       </c>
       <c r="E91" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="I91" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,36 +3925,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-152700</v>
+        <v>-343200</v>
       </c>
       <c r="E94" s="3">
-        <v>-326800</v>
+        <v>-151700</v>
       </c>
       <c r="F94" s="3">
-        <v>72900</v>
+        <v>-324800</v>
       </c>
       <c r="G94" s="3">
-        <v>686300</v>
+        <v>72400</v>
       </c>
       <c r="H94" s="3">
-        <v>89200</v>
+        <v>682000</v>
       </c>
       <c r="I94" s="3">
-        <v>-1332400</v>
+        <v>88600</v>
       </c>
       <c r="J94" s="3">
+        <v>-1324100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-653500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,36 +4153,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-40100</v>
+        <v>138900</v>
       </c>
       <c r="E100" s="3">
-        <v>268700</v>
+        <v>-39800</v>
       </c>
       <c r="F100" s="3">
-        <v>-190100</v>
+        <v>267000</v>
       </c>
       <c r="G100" s="3">
-        <v>-1069900</v>
+        <v>-188900</v>
       </c>
       <c r="H100" s="3">
+        <v>-1063200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
-        <v>1286900</v>
-      </c>
       <c r="J100" s="3">
+        <v>1278900</v>
+      </c>
+      <c r="K100" s="3">
         <v>596500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3950,36 +4195,39 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3989,36 +4237,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-63800</v>
+        <v>31700</v>
       </c>
       <c r="E102" s="3">
-        <v>37600</v>
+        <v>-63500</v>
       </c>
       <c r="F102" s="3">
-        <v>35500</v>
+        <v>37400</v>
       </c>
       <c r="G102" s="3">
-        <v>-202500</v>
+        <v>35300</v>
       </c>
       <c r="H102" s="3">
-        <v>274000</v>
+        <v>-201200</v>
       </c>
       <c r="I102" s="3">
-        <v>133100</v>
+        <v>272400</v>
       </c>
       <c r="J102" s="3">
+        <v>132200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>253800</v>
+        <v>259000</v>
       </c>
       <c r="E8" s="3">
-        <v>256300</v>
+        <v>261500</v>
       </c>
       <c r="F8" s="3">
-        <v>193200</v>
+        <v>197100</v>
       </c>
       <c r="G8" s="3">
-        <v>281100</v>
+        <v>286800</v>
       </c>
       <c r="H8" s="3">
-        <v>428100</v>
+        <v>436800</v>
       </c>
       <c r="I8" s="3">
-        <v>591500</v>
+        <v>603600</v>
       </c>
       <c r="J8" s="3">
-        <v>472900</v>
+        <v>482600</v>
       </c>
       <c r="K8" s="3">
         <v>187200</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>147400</v>
+        <v>150400</v>
       </c>
       <c r="E9" s="3">
-        <v>152800</v>
+        <v>155900</v>
       </c>
       <c r="F9" s="3">
-        <v>166000</v>
+        <v>169400</v>
       </c>
       <c r="G9" s="3">
-        <v>158400</v>
+        <v>161600</v>
       </c>
       <c r="H9" s="3">
-        <v>205000</v>
+        <v>209200</v>
       </c>
       <c r="I9" s="3">
-        <v>268500</v>
+        <v>273900</v>
       </c>
       <c r="J9" s="3">
-        <v>194800</v>
+        <v>198800</v>
       </c>
       <c r="K9" s="3">
         <v>61500</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>106400</v>
+        <v>108600</v>
       </c>
       <c r="E10" s="3">
-        <v>103500</v>
+        <v>105600</v>
       </c>
       <c r="F10" s="3">
-        <v>27200</v>
+        <v>27700</v>
       </c>
       <c r="G10" s="3">
-        <v>122700</v>
+        <v>125200</v>
       </c>
       <c r="H10" s="3">
-        <v>223100</v>
+        <v>227600</v>
       </c>
       <c r="I10" s="3">
-        <v>323000</v>
+        <v>329600</v>
       </c>
       <c r="J10" s="3">
-        <v>278100</v>
+        <v>283800</v>
       </c>
       <c r="K10" s="3">
         <v>125700</v>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -961,10 +961,10 @@
         <v>1700</v>
       </c>
       <c r="G14" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H14" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
         <v>1500</v>
       </c>
       <c r="I15" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J15" s="3">
         <v>1500</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>225400</v>
+        <v>230000</v>
       </c>
       <c r="E17" s="3">
-        <v>232400</v>
+        <v>237200</v>
       </c>
       <c r="F17" s="3">
-        <v>180200</v>
+        <v>183900</v>
       </c>
       <c r="G17" s="3">
-        <v>258600</v>
+        <v>263900</v>
       </c>
       <c r="H17" s="3">
-        <v>328500</v>
+        <v>335200</v>
       </c>
       <c r="I17" s="3">
-        <v>431500</v>
+        <v>440400</v>
       </c>
       <c r="J17" s="3">
-        <v>361200</v>
+        <v>368600</v>
       </c>
       <c r="K17" s="3">
         <v>147200</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>28400</v>
+        <v>29000</v>
       </c>
       <c r="E18" s="3">
-        <v>23800</v>
+        <v>24300</v>
       </c>
       <c r="F18" s="3">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="G18" s="3">
-        <v>22500</v>
+        <v>22900</v>
       </c>
       <c r="H18" s="3">
-        <v>99600</v>
+        <v>101600</v>
       </c>
       <c r="I18" s="3">
-        <v>160000</v>
+        <v>163200</v>
       </c>
       <c r="J18" s="3">
-        <v>111700</v>
+        <v>114000</v>
       </c>
       <c r="K18" s="3">
         <v>40000</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>28700</v>
+        <v>29200</v>
       </c>
       <c r="E21" s="3">
-        <v>24200</v>
+        <v>24600</v>
       </c>
       <c r="F21" s="3">
-        <v>13500</v>
+        <v>13800</v>
       </c>
       <c r="G21" s="3">
-        <v>23300</v>
+        <v>23800</v>
       </c>
       <c r="H21" s="3">
-        <v>101100</v>
+        <v>103200</v>
       </c>
       <c r="I21" s="3">
-        <v>161800</v>
+        <v>165100</v>
       </c>
       <c r="J21" s="3">
-        <v>113200</v>
+        <v>115500</v>
       </c>
       <c r="K21" s="3">
         <v>41000</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>28400</v>
+        <v>29000</v>
       </c>
       <c r="E23" s="3">
-        <v>23800</v>
+        <v>24300</v>
       </c>
       <c r="F23" s="3">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="G23" s="3">
-        <v>22500</v>
+        <v>22900</v>
       </c>
       <c r="H23" s="3">
-        <v>99600</v>
+        <v>101600</v>
       </c>
       <c r="I23" s="3">
-        <v>160000</v>
+        <v>163200</v>
       </c>
       <c r="J23" s="3">
-        <v>111700</v>
+        <v>114000</v>
       </c>
       <c r="K23" s="3">
         <v>40000</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="E24" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="F24" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G24" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="H24" s="3">
-        <v>25700</v>
+        <v>26300</v>
       </c>
       <c r="I24" s="3">
-        <v>41000</v>
+        <v>41800</v>
       </c>
       <c r="J24" s="3">
-        <v>38100</v>
+        <v>38900</v>
       </c>
       <c r="K24" s="3">
         <v>7300</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E26" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F26" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G26" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="H26" s="3">
-        <v>73900</v>
+        <v>75400</v>
       </c>
       <c r="I26" s="3">
-        <v>118900</v>
+        <v>121400</v>
       </c>
       <c r="J26" s="3">
-        <v>73600</v>
+        <v>75100</v>
       </c>
       <c r="K26" s="3">
         <v>32700</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E27" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F27" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G27" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="H27" s="3">
-        <v>73900</v>
+        <v>75400</v>
       </c>
       <c r="I27" s="3">
-        <v>118900</v>
+        <v>121400</v>
       </c>
       <c r="J27" s="3">
-        <v>73600</v>
+        <v>75100</v>
       </c>
       <c r="K27" s="3">
         <v>32700</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E33" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F33" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G33" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="H33" s="3">
-        <v>73900</v>
+        <v>75400</v>
       </c>
       <c r="I33" s="3">
-        <v>118900</v>
+        <v>121400</v>
       </c>
       <c r="J33" s="3">
-        <v>73600</v>
+        <v>75100</v>
       </c>
       <c r="K33" s="3">
         <v>32700</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E35" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F35" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G35" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="H35" s="3">
-        <v>73900</v>
+        <v>75400</v>
       </c>
       <c r="I35" s="3">
-        <v>118900</v>
+        <v>121400</v>
       </c>
       <c r="J35" s="3">
-        <v>73600</v>
+        <v>75100</v>
       </c>
       <c r="K35" s="3">
         <v>32700</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>249800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>314600</v>
+      </c>
+      <c r="G41" s="3">
         <v>276500</v>
       </c>
-      <c r="E41" s="3">
-        <v>244800</v>
-      </c>
-      <c r="F41" s="3">
-        <v>308300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>270900</v>
-      </c>
       <c r="H41" s="3">
-        <v>235600</v>
+        <v>240400</v>
       </c>
       <c r="I41" s="3">
-        <v>436800</v>
+        <v>445700</v>
       </c>
       <c r="J41" s="3">
-        <v>164500</v>
+        <v>167800</v>
       </c>
       <c r="K41" s="3">
         <v>32400</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1674600</v>
+        <v>1708800</v>
       </c>
       <c r="E47" s="3">
-        <v>1554300</v>
+        <v>1586000</v>
       </c>
       <c r="F47" s="3">
-        <v>1442400</v>
+        <v>1471800</v>
       </c>
       <c r="G47" s="3">
-        <v>1321000</v>
+        <v>1348000</v>
       </c>
       <c r="H47" s="3">
-        <v>1526100</v>
+        <v>1557200</v>
       </c>
       <c r="I47" s="3">
-        <v>2191000</v>
+        <v>2235800</v>
       </c>
       <c r="J47" s="3">
-        <v>2317200</v>
+        <v>2364500</v>
       </c>
       <c r="K47" s="3">
         <v>1025400</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="E48" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="F48" s="3">
         <v>2700</v>
       </c>
       <c r="G48" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="H48" s="3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="I48" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="J48" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="K48" s="3">
         <v>2600</v>
@@ -2253,7 +2253,7 @@
         <v>600</v>
       </c>
       <c r="G49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H49" s="3">
         <v>500</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12700</v>
+        <v>13000</v>
       </c>
       <c r="E52" s="3">
-        <v>10600</v>
+        <v>10800</v>
       </c>
       <c r="F52" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="G52" s="3">
-        <v>10500</v>
+        <v>10700</v>
       </c>
       <c r="H52" s="3">
         <v>2300</v>
       </c>
       <c r="I52" s="3">
-        <v>30100</v>
+        <v>30700</v>
       </c>
       <c r="J52" s="3">
-        <v>15500</v>
+        <v>15900</v>
       </c>
       <c r="K52" s="3">
         <v>7700</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2260900</v>
+        <v>2307000</v>
       </c>
       <c r="E54" s="3">
-        <v>2000800</v>
+        <v>2041700</v>
       </c>
       <c r="F54" s="3">
-        <v>1987600</v>
+        <v>2028200</v>
       </c>
       <c r="G54" s="3">
-        <v>1690200</v>
+        <v>1724700</v>
       </c>
       <c r="H54" s="3">
-        <v>1799700</v>
+        <v>1836400</v>
       </c>
       <c r="I54" s="3">
-        <v>2674000</v>
+        <v>2728600</v>
       </c>
       <c r="J54" s="3">
-        <v>2516700</v>
+        <v>2568100</v>
       </c>
       <c r="K54" s="3">
         <v>1085200</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>94900</v>
+        <v>96800</v>
       </c>
       <c r="E58" s="3">
-        <v>15600</v>
+        <v>15900</v>
       </c>
       <c r="F58" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="G58" s="3">
-        <v>70300</v>
+        <v>71700</v>
       </c>
       <c r="H58" s="3">
-        <v>120300</v>
+        <v>122800</v>
       </c>
       <c r="I58" s="3">
-        <v>582200</v>
+        <v>594100</v>
       </c>
       <c r="J58" s="3">
-        <v>485200</v>
+        <v>495100</v>
       </c>
       <c r="K58" s="3">
         <v>19700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>32200</v>
+        <v>32800</v>
       </c>
       <c r="E59" s="3">
-        <v>34100</v>
+        <v>34800</v>
       </c>
       <c r="F59" s="3">
-        <v>26900</v>
+        <v>27400</v>
       </c>
       <c r="G59" s="3">
-        <v>28200</v>
+        <v>28800</v>
       </c>
       <c r="H59" s="3">
-        <v>29300</v>
+        <v>29900</v>
       </c>
       <c r="I59" s="3">
-        <v>101100</v>
+        <v>103100</v>
       </c>
       <c r="J59" s="3">
-        <v>62500</v>
+        <v>63700</v>
       </c>
       <c r="K59" s="3">
         <v>20500</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1138900</v>
+        <v>1162200</v>
       </c>
       <c r="E61" s="3">
-        <v>1067600</v>
+        <v>1089400</v>
       </c>
       <c r="F61" s="3">
-        <v>1111100</v>
+        <v>1133700</v>
       </c>
       <c r="G61" s="3">
-        <v>780600</v>
+        <v>796500</v>
       </c>
       <c r="H61" s="3">
-        <v>919100</v>
+        <v>937800</v>
       </c>
       <c r="I61" s="3">
-        <v>1535100</v>
+        <v>1566400</v>
       </c>
       <c r="J61" s="3">
-        <v>1685000</v>
+        <v>1719400</v>
       </c>
       <c r="K61" s="3">
         <v>859700</v>
@@ -2742,19 +2742,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10000</v>
+        <v>10200</v>
       </c>
       <c r="E62" s="3">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="F62" s="3">
-        <v>21000</v>
+        <v>21400</v>
       </c>
       <c r="G62" s="3">
-        <v>54800</v>
+        <v>55900</v>
       </c>
       <c r="H62" s="3">
-        <v>49600</v>
+        <v>50700</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1707000</v>
+        <v>1741900</v>
       </c>
       <c r="E66" s="3">
-        <v>1463900</v>
+        <v>1493800</v>
       </c>
       <c r="F66" s="3">
-        <v>1460100</v>
+        <v>1489900</v>
       </c>
       <c r="G66" s="3">
-        <v>1173300</v>
+        <v>1197200</v>
       </c>
       <c r="H66" s="3">
-        <v>1302500</v>
+        <v>1329100</v>
       </c>
       <c r="I66" s="3">
-        <v>2253300</v>
+        <v>2299300</v>
       </c>
       <c r="J66" s="3">
-        <v>2263700</v>
+        <v>2309900</v>
       </c>
       <c r="K66" s="3">
         <v>929700</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>428800</v>
+        <v>437600</v>
       </c>
       <c r="E72" s="3">
-        <v>408800</v>
+        <v>417100</v>
       </c>
       <c r="F72" s="3">
-        <v>390200</v>
+        <v>398200</v>
       </c>
       <c r="G72" s="3">
-        <v>381200</v>
+        <v>389000</v>
       </c>
       <c r="H72" s="3">
-        <v>367800</v>
+        <v>375300</v>
       </c>
       <c r="I72" s="3">
-        <v>293900</v>
+        <v>299900</v>
       </c>
       <c r="J72" s="3">
-        <v>175000</v>
+        <v>178600</v>
       </c>
       <c r="K72" s="3">
         <v>102000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>553900</v>
+        <v>565200</v>
       </c>
       <c r="E76" s="3">
-        <v>536900</v>
+        <v>547800</v>
       </c>
       <c r="F76" s="3">
-        <v>527500</v>
+        <v>538300</v>
       </c>
       <c r="G76" s="3">
-        <v>516900</v>
+        <v>527400</v>
       </c>
       <c r="H76" s="3">
-        <v>497200</v>
+        <v>507300</v>
       </c>
       <c r="I76" s="3">
-        <v>420800</v>
+        <v>429400</v>
       </c>
       <c r="J76" s="3">
-        <v>253000</v>
+        <v>258200</v>
       </c>
       <c r="K76" s="3">
         <v>155500</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E81" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F81" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G81" s="3">
-        <v>15900</v>
+        <v>16200</v>
       </c>
       <c r="H81" s="3">
-        <v>73900</v>
+        <v>75400</v>
       </c>
       <c r="I81" s="3">
-        <v>118900</v>
+        <v>121400</v>
       </c>
       <c r="J81" s="3">
-        <v>73600</v>
+        <v>75100</v>
       </c>
       <c r="K81" s="3">
         <v>32700</v>
@@ -3506,13 +3506,13 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>1500</v>
       </c>
       <c r="I83" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J83" s="3">
         <v>1500</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>235700</v>
+        <v>240500</v>
       </c>
       <c r="E89" s="3">
-        <v>127000</v>
+        <v>129600</v>
       </c>
       <c r="F89" s="3">
-        <v>95300</v>
+        <v>97200</v>
       </c>
       <c r="G89" s="3">
-        <v>154700</v>
+        <v>157800</v>
       </c>
       <c r="H89" s="3">
-        <v>179500</v>
+        <v>183100</v>
       </c>
       <c r="I89" s="3">
-        <v>184100</v>
+        <v>187900</v>
       </c>
       <c r="J89" s="3">
-        <v>177800</v>
+        <v>181400</v>
       </c>
       <c r="K89" s="3">
         <v>52800</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-15800</v>
+        <v>-16100</v>
       </c>
       <c r="E91" s="3">
-        <v>-12400</v>
+        <v>-12700</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="H91" s="3">
         <v>-600</v>
       </c>
       <c r="I91" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="J91" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="K91" s="3">
         <v>-2100</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-343200</v>
+        <v>-350200</v>
       </c>
       <c r="E94" s="3">
-        <v>-151700</v>
+        <v>-154800</v>
       </c>
       <c r="F94" s="3">
-        <v>-324800</v>
+        <v>-331400</v>
       </c>
       <c r="G94" s="3">
-        <v>72400</v>
+        <v>73900</v>
       </c>
       <c r="H94" s="3">
-        <v>682000</v>
+        <v>695900</v>
       </c>
       <c r="I94" s="3">
-        <v>88600</v>
+        <v>90400</v>
       </c>
       <c r="J94" s="3">
-        <v>-1324100</v>
+        <v>-1351100</v>
       </c>
       <c r="K94" s="3">
         <v>-653500</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>138900</v>
+        <v>141800</v>
       </c>
       <c r="E100" s="3">
-        <v>-39800</v>
+        <v>-40600</v>
       </c>
       <c r="F100" s="3">
-        <v>267000</v>
+        <v>272500</v>
       </c>
       <c r="G100" s="3">
-        <v>-188900</v>
+        <v>-192700</v>
       </c>
       <c r="H100" s="3">
-        <v>-1063200</v>
+        <v>-1084900</v>
       </c>
       <c r="I100" s="3">
         <v>-400</v>
       </c>
       <c r="J100" s="3">
-        <v>1278900</v>
+        <v>1305000</v>
       </c>
       <c r="K100" s="3">
         <v>596500</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>31700</v>
+        <v>32300</v>
       </c>
       <c r="E102" s="3">
-        <v>-63500</v>
+        <v>-64700</v>
       </c>
       <c r="F102" s="3">
-        <v>37400</v>
+        <v>38100</v>
       </c>
       <c r="G102" s="3">
-        <v>35300</v>
+        <v>36000</v>
       </c>
       <c r="H102" s="3">
-        <v>-201200</v>
+        <v>-205300</v>
       </c>
       <c r="I102" s="3">
-        <v>272400</v>
+        <v>277900</v>
       </c>
       <c r="J102" s="3">
-        <v>132200</v>
+        <v>134900</v>
       </c>
       <c r="K102" s="3">
         <v>-3700</v>

--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>259000</v>
+        <v>119100</v>
       </c>
       <c r="E8" s="3">
-        <v>261500</v>
+        <v>100900</v>
       </c>
       <c r="F8" s="3">
-        <v>197100</v>
+        <v>139600</v>
       </c>
       <c r="G8" s="3">
-        <v>286800</v>
+        <v>155800</v>
       </c>
       <c r="H8" s="3">
-        <v>436800</v>
+        <v>204000</v>
       </c>
       <c r="I8" s="3">
-        <v>603600</v>
+        <v>276800</v>
       </c>
       <c r="J8" s="3">
-        <v>482600</v>
+        <v>261700</v>
       </c>
       <c r="K8" s="3">
         <v>187200</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>150400</v>
+        <v>48400</v>
       </c>
       <c r="E9" s="3">
-        <v>155900</v>
+        <v>46500</v>
       </c>
       <c r="F9" s="3">
-        <v>169400</v>
+        <v>67000</v>
       </c>
       <c r="G9" s="3">
-        <v>161600</v>
+        <v>63600</v>
       </c>
       <c r="H9" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>273900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>198800</v>
+        <v>25000</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>61500</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>108600</v>
+        <v>70700</v>
       </c>
       <c r="E10" s="3">
-        <v>105600</v>
+        <v>54400</v>
       </c>
       <c r="F10" s="3">
-        <v>27700</v>
+        <v>72600</v>
       </c>
       <c r="G10" s="3">
-        <v>125200</v>
+        <v>92300</v>
       </c>
       <c r="H10" s="3">
-        <v>227600</v>
+        <v>179000</v>
       </c>
       <c r="I10" s="3">
-        <v>329600</v>
+        <v>276800</v>
       </c>
       <c r="J10" s="3">
-        <v>283800</v>
+        <v>261700</v>
       </c>
       <c r="K10" s="3">
         <v>125700</v>
@@ -874,10 +874,10 @@
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G12" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
@@ -951,26 +951,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1100</v>
       </c>
       <c r="F14" s="3">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="G14" s="3">
-        <v>3500</v>
+        <v>5100</v>
       </c>
       <c r="H14" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K14" s="3">
         <v>7900</v>
@@ -1000,19 +1000,19 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>900</v>
       </c>
       <c r="H15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
         <v>1900</v>
       </c>
       <c r="J15" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="K15" s="3">
         <v>900</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>230000</v>
+        <v>101900</v>
       </c>
       <c r="E17" s="3">
-        <v>237200</v>
+        <v>84100</v>
       </c>
       <c r="F17" s="3">
-        <v>183900</v>
+        <v>122000</v>
       </c>
       <c r="G17" s="3">
-        <v>263900</v>
+        <v>125000</v>
       </c>
       <c r="H17" s="3">
-        <v>335200</v>
+        <v>96500</v>
       </c>
       <c r="I17" s="3">
-        <v>440400</v>
+        <v>105300</v>
       </c>
       <c r="J17" s="3">
-        <v>368600</v>
+        <v>137400</v>
       </c>
       <c r="K17" s="3">
         <v>147200</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>29000</v>
+        <v>17200</v>
       </c>
       <c r="E18" s="3">
-        <v>24300</v>
+        <v>16700</v>
       </c>
       <c r="F18" s="3">
-        <v>13200</v>
+        <v>17600</v>
       </c>
       <c r="G18" s="3">
-        <v>22900</v>
+        <v>30800</v>
       </c>
       <c r="H18" s="3">
-        <v>101600</v>
+        <v>107500</v>
       </c>
       <c r="I18" s="3">
-        <v>163200</v>
+        <v>171500</v>
       </c>
       <c r="J18" s="3">
-        <v>114000</v>
+        <v>124300</v>
       </c>
       <c r="K18" s="3">
         <v>40000</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>29200</v>
+        <v>17900</v>
       </c>
       <c r="E21" s="3">
-        <v>24600</v>
+        <v>18100</v>
       </c>
       <c r="F21" s="3">
-        <v>13800</v>
+        <v>18300</v>
       </c>
       <c r="G21" s="3">
-        <v>23800</v>
+        <v>30900</v>
       </c>
       <c r="H21" s="3">
-        <v>103200</v>
+        <v>109200</v>
       </c>
       <c r="I21" s="3">
-        <v>165100</v>
+        <v>173700</v>
       </c>
       <c r="J21" s="3">
-        <v>115500</v>
+        <v>125600</v>
       </c>
       <c r="K21" s="3">
         <v>41000</v>
@@ -1236,26 +1236,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1282,22 +1282,22 @@
         <v>29000</v>
       </c>
       <c r="E23" s="3">
-        <v>24300</v>
+        <v>25000</v>
       </c>
       <c r="F23" s="3">
-        <v>13200</v>
+        <v>14800</v>
       </c>
       <c r="G23" s="3">
-        <v>22900</v>
+        <v>24900</v>
       </c>
       <c r="H23" s="3">
-        <v>101600</v>
+        <v>103600</v>
       </c>
       <c r="I23" s="3">
-        <v>163200</v>
+        <v>168300</v>
       </c>
       <c r="J23" s="3">
-        <v>114000</v>
+        <v>124300</v>
       </c>
       <c r="K23" s="3">
         <v>40000</v>
@@ -1324,22 +1324,22 @@
         <v>5800</v>
       </c>
       <c r="E24" s="3">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="F24" s="3">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="G24" s="3">
-        <v>6700</v>
+        <v>7300</v>
       </c>
       <c r="H24" s="3">
-        <v>26300</v>
+        <v>26800</v>
       </c>
       <c r="I24" s="3">
-        <v>41800</v>
+        <v>43200</v>
       </c>
       <c r="J24" s="3">
-        <v>38900</v>
+        <v>42400</v>
       </c>
       <c r="K24" s="3">
         <v>7300</v>
@@ -1408,22 +1408,22 @@
         <v>23200</v>
       </c>
       <c r="E26" s="3">
-        <v>19100</v>
+        <v>19600</v>
       </c>
       <c r="F26" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="G26" s="3">
-        <v>16200</v>
+        <v>17600</v>
       </c>
       <c r="H26" s="3">
-        <v>75400</v>
+        <v>76800</v>
       </c>
       <c r="I26" s="3">
-        <v>121400</v>
+        <v>125200</v>
       </c>
       <c r="J26" s="3">
-        <v>75100</v>
+        <v>81900</v>
       </c>
       <c r="K26" s="3">
         <v>32700</v>
@@ -1450,22 +1450,22 @@
         <v>23200</v>
       </c>
       <c r="E27" s="3">
-        <v>19100</v>
+        <v>19600</v>
       </c>
       <c r="F27" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="G27" s="3">
-        <v>16200</v>
+        <v>17600</v>
       </c>
       <c r="H27" s="3">
-        <v>75400</v>
+        <v>76800</v>
       </c>
       <c r="I27" s="3">
-        <v>121400</v>
+        <v>125200</v>
       </c>
       <c r="J27" s="3">
-        <v>75100</v>
+        <v>81900</v>
       </c>
       <c r="K27" s="3">
         <v>32700</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1702,22 +1702,22 @@
         <v>23200</v>
       </c>
       <c r="E33" s="3">
-        <v>19100</v>
+        <v>19600</v>
       </c>
       <c r="F33" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="G33" s="3">
-        <v>16200</v>
+        <v>17600</v>
       </c>
       <c r="H33" s="3">
-        <v>75400</v>
+        <v>76800</v>
       </c>
       <c r="I33" s="3">
-        <v>121400</v>
+        <v>125200</v>
       </c>
       <c r="J33" s="3">
-        <v>75100</v>
+        <v>81900</v>
       </c>
       <c r="K33" s="3">
         <v>32700</v>
@@ -1786,22 +1786,22 @@
         <v>23200</v>
       </c>
       <c r="E35" s="3">
-        <v>19100</v>
+        <v>19600</v>
       </c>
       <c r="F35" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="G35" s="3">
-        <v>16200</v>
+        <v>17600</v>
       </c>
       <c r="H35" s="3">
-        <v>75400</v>
+        <v>76800</v>
       </c>
       <c r="I35" s="3">
-        <v>121400</v>
+        <v>125200</v>
       </c>
       <c r="J35" s="3">
-        <v>75100</v>
+        <v>81900</v>
       </c>
       <c r="K35" s="3">
         <v>32700</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>282200</v>
+        <v>282300</v>
       </c>
       <c r="E41" s="3">
-        <v>249800</v>
+        <v>256900</v>
       </c>
       <c r="F41" s="3">
-        <v>314600</v>
+        <v>351300</v>
       </c>
       <c r="G41" s="3">
-        <v>276500</v>
+        <v>300400</v>
       </c>
       <c r="H41" s="3">
-        <v>240400</v>
+        <v>244900</v>
       </c>
       <c r="I41" s="3">
-        <v>445700</v>
+        <v>459700</v>
       </c>
       <c r="J41" s="3">
-        <v>167800</v>
+        <v>182900</v>
       </c>
       <c r="K41" s="3">
         <v>32400</v>
@@ -1991,26 +1991,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1292300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1370800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1298600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1482000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2186400</v>
       </c>
       <c r="J43" s="3">
-        <v>1100</v>
+        <v>2507100</v>
       </c>
       <c r="K43" s="3">
         <v>2300</v>
@@ -2033,26 +2033,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2075,26 +2075,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>136300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>79100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>41900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="H45" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>27900</v>
       </c>
       <c r="J45" s="3">
-        <v>1800</v>
+        <v>26700</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>2102100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1895800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1936400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1707000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1747800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>2674100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>2716800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1708800</v>
+        <v>63800</v>
       </c>
       <c r="E47" s="3">
-        <v>1586000</v>
+        <v>82300</v>
       </c>
       <c r="F47" s="3">
-        <v>1471800</v>
+        <v>175100</v>
       </c>
       <c r="G47" s="3">
-        <v>1348000</v>
+        <v>69300</v>
       </c>
       <c r="H47" s="3">
-        <v>1557200</v>
+        <v>98900</v>
       </c>
       <c r="I47" s="3">
-        <v>2235800</v>
+        <v>105000</v>
       </c>
       <c r="J47" s="3">
-        <v>2364500</v>
+        <v>61500</v>
       </c>
       <c r="K47" s="3">
         <v>1025400</v>
@@ -2205,22 +2205,22 @@
         <v>5100</v>
       </c>
       <c r="E48" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="F48" s="3">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="3">
-        <v>3400</v>
+        <v>3700</v>
       </c>
       <c r="H48" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="I48" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="J48" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="K48" s="3">
         <v>2600</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13000</v>
+        <v>123400</v>
       </c>
       <c r="E52" s="3">
-        <v>10800</v>
+        <v>105300</v>
       </c>
       <c r="F52" s="3">
-        <v>3000</v>
+        <v>146100</v>
       </c>
       <c r="G52" s="3">
-        <v>10700</v>
+        <v>81700</v>
       </c>
       <c r="H52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>30700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15900</v>
+        <v>14400</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>7700</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2307000</v>
+        <v>2307800</v>
       </c>
       <c r="E54" s="3">
-        <v>2041700</v>
+        <v>2099700</v>
       </c>
       <c r="F54" s="3">
-        <v>2028200</v>
+        <v>2264600</v>
       </c>
       <c r="G54" s="3">
-        <v>1724700</v>
+        <v>1873800</v>
       </c>
       <c r="H54" s="3">
-        <v>1836400</v>
+        <v>1870800</v>
       </c>
       <c r="I54" s="3">
-        <v>2728600</v>
+        <v>2814100</v>
       </c>
       <c r="J54" s="3">
-        <v>2568100</v>
+        <v>2799600</v>
       </c>
       <c r="K54" s="3">
         <v>1085200</v>
@@ -2531,26 +2531,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>96800</v>
+        <v>1005200</v>
       </c>
       <c r="E58" s="3">
-        <v>15900</v>
+        <v>839200</v>
       </c>
       <c r="F58" s="3">
-        <v>6400</v>
+        <v>739800</v>
       </c>
       <c r="G58" s="3">
-        <v>71700</v>
+        <v>614200</v>
       </c>
       <c r="H58" s="3">
-        <v>122800</v>
+        <v>777600</v>
       </c>
       <c r="I58" s="3">
-        <v>594100</v>
+        <v>1246200</v>
       </c>
       <c r="J58" s="3">
-        <v>495100</v>
+        <v>1850000</v>
       </c>
       <c r="K58" s="3">
         <v>19700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>32800</v>
+        <v>26000</v>
       </c>
       <c r="E59" s="3">
-        <v>34800</v>
+        <v>28500</v>
       </c>
       <c r="F59" s="3">
-        <v>27400</v>
+        <v>24800</v>
       </c>
       <c r="G59" s="3">
-        <v>28800</v>
+        <v>24500</v>
       </c>
       <c r="H59" s="3">
-        <v>29900</v>
+        <v>20400</v>
       </c>
       <c r="I59" s="3">
-        <v>103100</v>
+        <v>101000</v>
       </c>
       <c r="J59" s="3">
-        <v>63700</v>
+        <v>61600</v>
       </c>
       <c r="K59" s="3">
         <v>20500</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1045300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>885600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>780500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>656000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>822300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1368400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1935500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1162200</v>
+        <v>257900</v>
       </c>
       <c r="E61" s="3">
-        <v>1089400</v>
+        <v>301700</v>
       </c>
       <c r="F61" s="3">
-        <v>1133700</v>
+        <v>535700</v>
       </c>
       <c r="G61" s="3">
-        <v>796500</v>
+        <v>332100</v>
       </c>
       <c r="H61" s="3">
-        <v>937800</v>
+        <v>308300</v>
       </c>
       <c r="I61" s="3">
-        <v>1566400</v>
+        <v>982000</v>
       </c>
       <c r="J61" s="3">
-        <v>1719400</v>
+        <v>564100</v>
       </c>
       <c r="K61" s="3">
         <v>859700</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10200</v>
+        <v>423400</v>
       </c>
       <c r="E62" s="3">
-        <v>10400</v>
+        <v>325700</v>
       </c>
       <c r="F62" s="3">
-        <v>21400</v>
+        <v>315100</v>
       </c>
       <c r="G62" s="3">
-        <v>55900</v>
+        <v>233400</v>
       </c>
       <c r="H62" s="3">
-        <v>50700</v>
+        <v>154800</v>
       </c>
       <c r="I62" s="3">
-        <v>200</v>
+        <v>14400</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>17400</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1741900</v>
+        <v>1742400</v>
       </c>
       <c r="E66" s="3">
-        <v>1493800</v>
+        <v>1528800</v>
       </c>
       <c r="F66" s="3">
-        <v>1489900</v>
+        <v>1663600</v>
       </c>
       <c r="G66" s="3">
-        <v>1197200</v>
+        <v>1300800</v>
       </c>
       <c r="H66" s="3">
-        <v>1329100</v>
+        <v>1354000</v>
       </c>
       <c r="I66" s="3">
-        <v>2299300</v>
+        <v>2371300</v>
       </c>
       <c r="J66" s="3">
-        <v>2309900</v>
+        <v>2518100</v>
       </c>
       <c r="K66" s="3">
         <v>929700</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>437600</v>
+        <v>437700</v>
       </c>
       <c r="E72" s="3">
-        <v>417100</v>
+        <v>429000</v>
       </c>
       <c r="F72" s="3">
-        <v>398200</v>
+        <v>444600</v>
       </c>
       <c r="G72" s="3">
-        <v>389000</v>
+        <v>422600</v>
       </c>
       <c r="H72" s="3">
-        <v>375300</v>
+        <v>382300</v>
       </c>
       <c r="I72" s="3">
-        <v>299900</v>
+        <v>309300</v>
       </c>
       <c r="J72" s="3">
-        <v>178600</v>
+        <v>194700</v>
       </c>
       <c r="K72" s="3">
         <v>102000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>565200</v>
+        <v>565400</v>
       </c>
       <c r="E76" s="3">
-        <v>547800</v>
+        <v>563400</v>
       </c>
       <c r="F76" s="3">
-        <v>538300</v>
+        <v>601100</v>
       </c>
       <c r="G76" s="3">
-        <v>527400</v>
+        <v>573100</v>
       </c>
       <c r="H76" s="3">
-        <v>507300</v>
+        <v>516800</v>
       </c>
       <c r="I76" s="3">
-        <v>429400</v>
+        <v>442800</v>
       </c>
       <c r="J76" s="3">
-        <v>258200</v>
+        <v>281400</v>
       </c>
       <c r="K76" s="3">
         <v>155500</v>
@@ -3440,22 +3440,22 @@
         <v>23200</v>
       </c>
       <c r="E81" s="3">
-        <v>19100</v>
+        <v>19600</v>
       </c>
       <c r="F81" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="G81" s="3">
-        <v>16200</v>
+        <v>17600</v>
       </c>
       <c r="H81" s="3">
-        <v>75400</v>
+        <v>76800</v>
       </c>
       <c r="I81" s="3">
-        <v>121400</v>
+        <v>125200</v>
       </c>
       <c r="J81" s="3">
-        <v>75100</v>
+        <v>81900</v>
       </c>
       <c r="K81" s="3">
         <v>32700</v>
@@ -3503,19 +3503,19 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I83" s="3">
         <v>1900</v>
       </c>
       <c r="J83" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>240500</v>
+        <v>240600</v>
       </c>
       <c r="E89" s="3">
-        <v>129600</v>
+        <v>133300</v>
       </c>
       <c r="F89" s="3">
-        <v>97200</v>
+        <v>108600</v>
       </c>
       <c r="G89" s="3">
-        <v>157800</v>
+        <v>171500</v>
       </c>
       <c r="H89" s="3">
-        <v>183100</v>
+        <v>186600</v>
       </c>
       <c r="I89" s="3">
-        <v>187900</v>
+        <v>192600</v>
       </c>
       <c r="J89" s="3">
-        <v>181400</v>
+        <v>197700</v>
       </c>
       <c r="K89" s="3">
         <v>52800</v>
@@ -3812,10 +3812,10 @@
         <v>-16100</v>
       </c>
       <c r="E91" s="3">
-        <v>-12700</v>
+        <v>-13000</v>
       </c>
       <c r="F91" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="G91" s="3">
         <v>-500</v>
@@ -3824,10 +3824,10 @@
         <v>-600</v>
       </c>
       <c r="I91" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="J91" s="3">
-        <v>-2800</v>
+        <v>-3000</v>
       </c>
       <c r="K91" s="3">
         <v>-2100</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-350200</v>
+        <v>-350300</v>
       </c>
       <c r="E94" s="3">
-        <v>-154800</v>
+        <v>-159200</v>
       </c>
       <c r="F94" s="3">
-        <v>-331400</v>
+        <v>-370000</v>
       </c>
       <c r="G94" s="3">
-        <v>73900</v>
+        <v>80300</v>
       </c>
       <c r="H94" s="3">
-        <v>695900</v>
+        <v>709000</v>
       </c>
       <c r="I94" s="3">
-        <v>90400</v>
+        <v>94400</v>
       </c>
       <c r="J94" s="3">
-        <v>-1351100</v>
+        <v>-1472900</v>
       </c>
       <c r="K94" s="3">
         <v>-653500</v>
@@ -4166,22 +4166,22 @@
         <v>141800</v>
       </c>
       <c r="E100" s="3">
-        <v>-40600</v>
+        <v>-41800</v>
       </c>
       <c r="F100" s="3">
-        <v>272500</v>
+        <v>304200</v>
       </c>
       <c r="G100" s="3">
-        <v>-192700</v>
+        <v>-209400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1084900</v>
+        <v>-1105200</v>
       </c>
       <c r="I100" s="3">
         <v>-400</v>
       </c>
       <c r="J100" s="3">
-        <v>1305000</v>
+        <v>1422600</v>
       </c>
       <c r="K100" s="3">
         <v>596500</v>
@@ -4214,10 +4214,10 @@
         <v>-200</v>
       </c>
       <c r="G101" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="H101" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>32300</v>
+        <v>32400</v>
       </c>
       <c r="E102" s="3">
-        <v>-64700</v>
+        <v>-66600</v>
       </c>
       <c r="F102" s="3">
-        <v>38100</v>
+        <v>42600</v>
       </c>
       <c r="G102" s="3">
-        <v>36000</v>
+        <v>39100</v>
       </c>
       <c r="H102" s="3">
-        <v>-205300</v>
+        <v>-209200</v>
       </c>
       <c r="I102" s="3">
-        <v>277900</v>
+        <v>286600</v>
       </c>
       <c r="J102" s="3">
-        <v>134900</v>
+        <v>147100</v>
       </c>
       <c r="K102" s="3">
         <v>-3700</v>

--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E8" s="3">
         <v>119100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>100900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>139600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>155800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>276800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>261700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E9" s="3">
         <v>48400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>67000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>63600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>61500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E10" s="3">
         <v>70700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>72600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>92300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>179000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>276800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>261700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>125700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +874,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,39 +961,42 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="E14" s="3">
         <v>1100</v>
       </c>
       <c r="F14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,39 +1006,42 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E17" s="3">
         <v>101900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>84100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>122000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>125000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>96500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>105300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>137400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>147200</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>17200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>107500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>171500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>124300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,37 +1179,38 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1188,39 +1221,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E21" s="3">
         <v>17900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>30900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>109200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>173700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>125600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>41000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1266,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,8 +1296,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>29000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>103600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>168300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>124300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>40000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>43200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>23200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>125200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>23200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>125200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,38 +1716,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>23200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>76800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>23200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>76800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,38 +1987,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E41" s="3">
         <v>282300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>256900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>351300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>244900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>459700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>182900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,9 +2029,12 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,39 +2074,42 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1016900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1335000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1292300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1370800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1298600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1482000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2186400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2507100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2149,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E45" s="3">
         <v>136300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>79100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2209,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1817600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2102100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1895800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1936400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1707000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1747800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2674100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2716800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E47" s="3">
         <v>63800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>82300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>175100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>69300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>98900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>105000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1025400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,9 +2344,12 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2247,29 +2357,29 @@
         <v>400</v>
       </c>
       <c r="E49" s="3">
+        <v>400</v>
+      </c>
+      <c r="F49" s="3">
         <v>500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>500</v>
       </c>
       <c r="H49" s="3">
         <v>500</v>
       </c>
       <c r="I49" s="3">
+        <v>500</v>
+      </c>
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>400</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E52" s="3">
         <v>123400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>105300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>146100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>81700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>7700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,39 +2569,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2058800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2307800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2099700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2264600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1873800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1870800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2814100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2799600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1085200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,8 +2655,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2552,8 +2682,8 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2567,81 +2697,87 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1005200</v>
+        <v>962300</v>
       </c>
       <c r="E58" s="3">
+        <v>1003400</v>
+      </c>
+      <c r="F58" s="3">
         <v>839200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>739800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>614200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>777600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1246200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1850000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E59" s="3">
         <v>26000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>101000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2787,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1045300</v>
+        <v>1001600</v>
       </c>
       <c r="E60" s="3">
+        <v>1043500</v>
+      </c>
+      <c r="F60" s="3">
         <v>885600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>780500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>656000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>822300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1368400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1935500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2693,39 +2832,42 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>257900</v>
+        <v>82200</v>
       </c>
       <c r="E61" s="3">
+        <v>259700</v>
+      </c>
+      <c r="F61" s="3">
         <v>301700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>535700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>332100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>308300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>982000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>564100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>859700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2735,39 +2877,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>404900</v>
+      </c>
+      <c r="E62" s="3">
         <v>423400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>325700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>315100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>233400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>154800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1502900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1742400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1528800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1663600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1354000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2371300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2518100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>929700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,39 +3301,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>430400</v>
+      </c>
+      <c r="E72" s="3">
         <v>437700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>429000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>444600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>422600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>382300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>309300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>194700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>102000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,39 +3481,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>555900</v>
+      </c>
+      <c r="E76" s="3">
         <v>565400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>563400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>601100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>573100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>516800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>442800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>281400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>155500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>23200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>76800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3688,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3955,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E89" s="3">
         <v>240600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>133300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>108600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>171500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>186600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>192600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>197700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>52800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4022,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-350300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-159200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-370000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>80300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>709000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>94400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1472900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-653500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4398,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-182500</v>
+      </c>
+      <c r="E100" s="3">
         <v>141800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>304200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-209400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1105200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1422600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>596500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,39 +4443,42 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,39 +4488,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-113900</v>
+      </c>
+      <c r="E102" s="3">
         <v>32400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-66600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>42600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-209200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>286600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>147100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>85700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>119100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>139600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>155800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>276800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>261700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E9" s="3">
         <v>34600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>63600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>61500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E10" s="3">
         <v>51000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>72600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>92300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>179000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>276800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>261700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>125700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,41 +887,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,42 +980,45 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1100</v>
       </c>
       <c r="F14" s="3">
         <v>1100</v>
       </c>
       <c r="G14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,42 +1028,45 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E17" s="3">
         <v>90600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>101900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>84100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>122000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>125000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>96500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>105300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>147200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>30800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>107500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>171500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>124300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,8 +1212,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1189,31 +1222,31 @@
         <v>-800</v>
       </c>
       <c r="E20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1224,42 +1257,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>109200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>173700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>125600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>41000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,9 +1305,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1299,8 +1338,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="E23" s="3">
         <v>6600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>103600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>168300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>124300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>43200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>125200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>76800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>125200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,9 +1785,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1729,31 +1798,31 @@
         <v>800</v>
       </c>
       <c r="E32" s="3">
+        <v>800</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>76800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>76800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,41 +2073,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E41" s="3">
         <v>160300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>256900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>351300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>244900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>459700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>182900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,9 +2118,12 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2077,42 +2166,45 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>416100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1016900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1335000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1292300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1370800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1298600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1482000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2186400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2507100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2152,8 +2247,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E45" s="3">
         <v>156800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>136300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>79100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,39 +2310,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1817600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2102100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1895800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1936400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1707000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1747800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2674100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2716800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E47" s="3">
         <v>38400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>82300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>175100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>69300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>105000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1025400</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E48" s="3">
         <v>29100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,42 +2454,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>400</v>
       </c>
       <c r="F49" s="3">
+        <v>400</v>
+      </c>
+      <c r="G49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>500</v>
       </c>
       <c r="I49" s="3">
         <v>500</v>
       </c>
       <c r="J49" s="3">
+        <v>500</v>
+      </c>
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E52" s="3">
         <v>155300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>123400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>105300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>146100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>81700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>7700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,42 +2694,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1465300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2058800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2307800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2099700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2264600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1873800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1870800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2814100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2799600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1085200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,8 +2785,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2685,8 +2815,8 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2700,87 +2830,93 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E58" s="3">
         <v>962300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1003400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>839200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>739800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>614200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>777600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1246200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1850000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E59" s="3">
         <v>28700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>101000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,39 +2926,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>501700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1001600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1043500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>885600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>780500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>656000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>822300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1368400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1935500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2835,42 +2974,45 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E61" s="3">
         <v>82200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>259700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>301700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>535700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>332100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>308300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>982000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>564100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>859700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2880,42 +3022,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E62" s="3">
         <v>404900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>423400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>325700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>315100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>233400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>154800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>953400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1502900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1742400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1528800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1663600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1354000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2371300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2518100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>929700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,42 +3474,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>381900</v>
+      </c>
+      <c r="E72" s="3">
         <v>430400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>437700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>429000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>444600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>422600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>382300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>309300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>194700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>102000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,42 +3666,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E76" s="3">
         <v>555900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>565400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>563400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>601100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>573100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>516800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>442800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>281400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>155500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>76800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,41 +3886,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,42 +4171,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E89" s="3">
         <v>103700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>240600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>133300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>108600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>171500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>186600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>192600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>197700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>52800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,41 +4242,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>468100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-350300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-159200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-370000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>80300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>709000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>94400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1472900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-653500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,42 +4643,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-598400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-182500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>141800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-41800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>304200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-209400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1105200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1422600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>596500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,42 +4691,45 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,42 +4739,45 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-113900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-66600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>42600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-209200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>286600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>147100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
